--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Fiets.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_concproduct_Fiets.xlsx
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>413.9612067934759</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <v>294.3585856825257</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>248.7800367579857</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>230.6370800733492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>2113.850600438588</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>1495.657357800417</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>1295.065367782165</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>1168.291416864006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>196.0768590149286</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <v>135.5174981927554</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>116.9382027048995</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>105.387987227163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>34.9856855235868</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <v>22.87120849966348</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>19.47136745963189</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>18.93101564496777</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>109.3799209453937</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <v>74.84677731521121</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>65.12455326262716</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>59.37250690201903</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
